--- a/data_lake/bart_temp_med/dt=2026-10-25/temperaturamed.xlsx
+++ b/data_lake/bart_temp_med/dt=2026-10-25/temperaturamed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E46E9F4-6B8F-4A2D-A855-0F61D0BB281B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F53EBE-D34B-4D44-B191-282CD1D485A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AF$1:$AG$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AH$1:$AH$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6354,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="201" width="32.42578125" style="50" customWidth="1"/>
-    <col min="202" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="202" width="32.42578125" style="50" customWidth="1"/>
+    <col min="203" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6705,7 +6705,9 @@
       <c r="AG5" s="56">
         <v>28.3</v>
       </c>
-      <c r="AH5" s="56"/>
+      <c r="AH5" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AI5" s="56"/>
       <c r="AJ5" s="56"/>
       <c r="AK5" s="56"/>
@@ -6715,11 +6717,11 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>29.154545454545449</v>
+        <v>29.139130434782601</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6727,7 +6729,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>1.2735448243512799</v>
+        <v>1.2581298045884317</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6830,7 +6832,9 @@
       <c r="AG6" s="56">
         <v>26.7</v>
       </c>
-      <c r="AH6" s="56"/>
+      <c r="AH6" s="56">
+        <v>29.1</v>
+      </c>
       <c r="AI6" s="56"/>
       <c r="AJ6" s="56"/>
       <c r="AK6" s="56"/>
@@ -6840,11 +6844,11 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.834782608695654</v>
+        <v>28.845833333333335</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6852,7 +6856,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>1.105153218014653</v>
+        <v>1.1162039426523336</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6955,7 +6959,9 @@
       <c r="AG7" s="56">
         <v>31</v>
       </c>
-      <c r="AH7" s="56"/>
+      <c r="AH7" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AI7" s="56"/>
       <c r="AJ7" s="56"/>
       <c r="AK7" s="56"/>
@@ -6965,11 +6971,11 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>29.860869565217396</v>
+        <v>29.758333333333336</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6977,7 +6983,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>1.6817524582657768</v>
+        <v>1.5792162263817175</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7205,7 +7211,9 @@
       <c r="AG9" s="56">
         <v>30.2</v>
       </c>
-      <c r="AH9" s="56"/>
+      <c r="AH9" s="56">
+        <v>25.8</v>
+      </c>
       <c r="AI9" s="56"/>
       <c r="AJ9" s="56"/>
       <c r="AK9" s="56"/>
@@ -7215,11 +7223,11 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.19130434782609</v>
+        <v>29.05</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7227,7 +7235,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>8.7455781517888909E-2</v>
+        <v>-5.3848566308200674E-2</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7326,7 +7334,9 @@
       <c r="AG10" s="56">
         <v>29.2</v>
       </c>
-      <c r="AH10" s="56"/>
+      <c r="AH10" s="56">
+        <v>29.5</v>
+      </c>
       <c r="AI10" s="56"/>
       <c r="AJ10" s="56"/>
       <c r="AK10" s="56"/>
@@ -7336,11 +7346,11 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>29.852380952380958</v>
+        <v>29.83636363636364</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7348,7 +7358,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.72968211298857</v>
+        <v>1.7136647969712513</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7451,7 +7461,9 @@
       <c r="AG11" s="56">
         <v>30.3</v>
       </c>
-      <c r="AH11" s="56"/>
+      <c r="AH11" s="56">
+        <v>28.4</v>
+      </c>
       <c r="AI11" s="56"/>
       <c r="AJ11" s="56"/>
       <c r="AK11" s="56"/>
@@ -7461,11 +7473,11 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>29.021739130434778</v>
+        <v>28.995833333333326</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7473,7 +7485,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>1.3120023718976164</v>
+        <v>1.286096574796165</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7574,7 +7586,9 @@
       <c r="AG12" s="56">
         <v>29.9</v>
       </c>
-      <c r="AH12" s="56"/>
+      <c r="AH12" s="56">
+        <v>24.7</v>
+      </c>
       <c r="AI12" s="56"/>
       <c r="AJ12" s="56"/>
       <c r="AK12" s="56"/>
@@ -7584,11 +7598,11 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>28.713636363636365</v>
+        <v>28.539130434782614</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7596,7 +7610,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>1.1556395113250062</v>
+        <v>0.98113358247125504</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7699,7 +7713,9 @@
       <c r="AG13" s="56">
         <v>30.5</v>
       </c>
-      <c r="AH13" s="56"/>
+      <c r="AH13" s="56">
+        <v>26.5</v>
+      </c>
       <c r="AI13" s="56"/>
       <c r="AJ13" s="56"/>
       <c r="AK13" s="56"/>
@@ -7709,11 +7725,11 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>28.182608695652174</v>
+        <v>28.112500000000001</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7721,7 +7737,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>0.79997428705005547</v>
+        <v>0.72986559139788199</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7824,7 +7840,9 @@
       <c r="AG14" s="56">
         <v>24.7</v>
       </c>
-      <c r="AH14" s="56"/>
+      <c r="AH14" s="56">
+        <v>21.9</v>
+      </c>
       <c r="AI14" s="56"/>
       <c r="AJ14" s="56"/>
       <c r="AK14" s="56"/>
@@ -7834,11 +7852,11 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.2304347826087</v>
+        <v>23.175000000000001</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7846,7 +7864,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>1.9713869218672997</v>
+        <v>1.9159521392586001</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7949,7 +7967,9 @@
       <c r="AG15" s="56">
         <v>32</v>
       </c>
-      <c r="AH15" s="56"/>
+      <c r="AH15" s="56">
+        <v>30.5</v>
+      </c>
       <c r="AI15" s="56"/>
       <c r="AJ15" s="56"/>
       <c r="AK15" s="56"/>
@@ -7959,11 +7979,11 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.991304347826084</v>
+        <v>30.012499999999999</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7971,7 +7991,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>2.3182571128030531</v>
+        <v>2.3394527649769685</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8074,7 +8094,9 @@
       <c r="AG16" s="56">
         <v>28.4</v>
       </c>
-      <c r="AH16" s="56"/>
+      <c r="AH16" s="56">
+        <v>27</v>
+      </c>
       <c r="AI16" s="56"/>
       <c r="AJ16" s="56"/>
       <c r="AK16" s="56"/>
@@ -8084,11 +8106,11 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>27.92173913043478</v>
+        <v>27.883333333333329</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8096,7 +8118,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.71347045803135956</v>
+        <v>0.67506466092990891</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8199,7 +8221,9 @@
       <c r="AG17" s="56">
         <v>24</v>
       </c>
-      <c r="AH17" s="56"/>
+      <c r="AH17" s="56">
+        <v>22.3</v>
+      </c>
       <c r="AI17" s="56"/>
       <c r="AJ17" s="56"/>
       <c r="AK17" s="56"/>
@@ -8209,11 +8233,11 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>22.95652173913043</v>
+        <v>22.92916666666666</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8221,7 +8245,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.75060961454757091</v>
+        <v>0.7232545420838008</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8324,7 +8348,9 @@
       <c r="AG18" s="56">
         <v>19.899999999999999</v>
       </c>
-      <c r="AH18" s="56"/>
+      <c r="AH18" s="56">
+        <v>18.3</v>
+      </c>
       <c r="AI18" s="56"/>
       <c r="AJ18" s="56"/>
       <c r="AK18" s="56"/>
@@ -8334,11 +8360,11 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.208695652173912</v>
+        <v>18.212500000000002</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8346,7 +8372,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.5063627473897512</v>
+        <v>1.5101670952158415</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8449,7 +8475,9 @@
       <c r="AG19" s="56">
         <v>24.9</v>
       </c>
-      <c r="AH19" s="56"/>
+      <c r="AH19" s="56">
+        <v>23.7</v>
+      </c>
       <c r="AI19" s="56"/>
       <c r="AJ19" s="56"/>
       <c r="AK19" s="56"/>
@@ -8459,11 +8487,11 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>22.791304347826095</v>
+        <v>22.829166666666676</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8471,7 +8499,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>1.5133809607293252</v>
+        <v>1.5512432795699063</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8574,7 +8602,9 @@
       <c r="AG20" s="56">
         <v>24.3</v>
       </c>
-      <c r="AH20" s="56"/>
+      <c r="AH20" s="56">
+        <v>22.8</v>
+      </c>
       <c r="AI20" s="56"/>
       <c r="AJ20" s="56"/>
       <c r="AK20" s="56"/>
@@ -8584,11 +8614,11 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>22.969565217391306</v>
+        <v>22.962500000000002</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8596,7 +8626,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>1.3619894598155575</v>
+        <v>1.3549242424242536</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8699,7 +8729,9 @@
       <c r="AG21" s="56">
         <v>28</v>
       </c>
-      <c r="AH21" s="56"/>
+      <c r="AH21" s="56">
+        <v>26.2</v>
+      </c>
       <c r="AI21" s="56"/>
       <c r="AJ21" s="56"/>
       <c r="AK21" s="56"/>
@@ -8709,11 +8741,11 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>25.35217391304348</v>
+        <v>25.387500000000003</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8721,7 +8753,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>1.6974835163063702</v>
+        <v>1.7328096032628935</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8824,7 +8856,9 @@
       <c r="AG22" s="56">
         <v>17.100000000000001</v>
       </c>
-      <c r="AH22" s="56"/>
+      <c r="AH22" s="56">
+        <v>16</v>
+      </c>
       <c r="AI22" s="56"/>
       <c r="AJ22" s="56"/>
       <c r="AK22" s="56"/>
@@ -8834,11 +8868,11 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>16.069565217391307</v>
+        <v>16.06666666666667</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8846,7 +8880,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>2.3200970914312578</v>
+        <v>2.3171985407066202</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8949,7 +8983,9 @@
       <c r="AG23" s="56">
         <v>26.1</v>
       </c>
-      <c r="AH23" s="56"/>
+      <c r="AH23" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AI23" s="56"/>
       <c r="AJ23" s="56"/>
       <c r="AK23" s="56"/>
@@ -8959,11 +8995,11 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>24.586956521739125</v>
+        <v>24.658333333333328</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9074,7 +9110,9 @@
       <c r="AG24" s="56">
         <v>33</v>
       </c>
-      <c r="AH24" s="56"/>
+      <c r="AH24" s="56">
+        <v>31.1</v>
+      </c>
       <c r="AI24" s="56"/>
       <c r="AJ24" s="56"/>
       <c r="AK24" s="56"/>
@@ -9084,11 +9122,11 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>30.117391304347827</v>
+        <v>30.158333333333335</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9096,7 +9134,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>1.8635773855903679</v>
+        <v>1.9045194145758764</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9199,7 +9237,9 @@
       <c r="AG25" s="56">
         <v>20.6</v>
       </c>
-      <c r="AH25" s="56"/>
+      <c r="AH25" s="56">
+        <v>20.7</v>
+      </c>
       <c r="AI25" s="56"/>
       <c r="AJ25" s="56"/>
       <c r="AK25" s="56"/>
@@ -9209,11 +9249,11 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>20.304347826086961</v>
+        <v>20.320833333333336</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9221,7 +9261,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>1.3182439166361917</v>
+        <v>1.3347294238825675</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9324,7 +9364,9 @@
       <c r="AG26" s="56">
         <v>13.6</v>
       </c>
-      <c r="AH26" s="56"/>
+      <c r="AH26" s="56">
+        <v>13.1</v>
+      </c>
       <c r="AI26" s="56"/>
       <c r="AJ26" s="56"/>
       <c r="AK26" s="56"/>
@@ -9334,11 +9376,11 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>13.026086956521738</v>
+        <v>13.029166666666667</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9346,7 +9388,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.6639325786415871</v>
+        <v>1.6670122887865162</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9449,7 +9491,9 @@
       <c r="AG27" s="56">
         <v>27.5</v>
       </c>
-      <c r="AH27" s="56"/>
+      <c r="AH27" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AI27" s="56"/>
       <c r="AJ27" s="56"/>
       <c r="AK27" s="56"/>
@@ -9459,11 +9503,11 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>27.339130434782611</v>
+        <v>27.341666666666669</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9471,7 +9515,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>0.91064044590608972</v>
+        <v>0.91317667779014755</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9574,7 +9618,9 @@
       <c r="AG28" s="56">
         <v>29.7</v>
       </c>
-      <c r="AH28" s="99"/>
+      <c r="AH28" s="99">
+        <v>27.5</v>
+      </c>
       <c r="AI28" s="56"/>
       <c r="AJ28" s="56"/>
       <c r="AK28" s="56"/>
@@ -9584,11 +9630,11 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>28.721739130434784</v>
+        <v>28.670833333333334</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9596,7 +9642,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>1.8639446868561045</v>
+        <v>1.8130388897546545</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9699,7 +9745,9 @@
       <c r="AG29" s="56">
         <v>30.4</v>
       </c>
-      <c r="AH29" s="56"/>
+      <c r="AH29" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AI29" s="56"/>
       <c r="AJ29" s="56"/>
       <c r="AK29" s="56"/>
@@ -9709,11 +9757,11 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>29.373913043478261</v>
+        <v>29.383333333333336</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9721,7 +9769,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>1.0027228321323598</v>
+        <v>1.0121431219874353</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9824,7 +9872,9 @@
       <c r="AG30" s="56">
         <v>28.2</v>
       </c>
-      <c r="AH30" s="56"/>
+      <c r="AH30" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AI30" s="56"/>
       <c r="AJ30" s="56"/>
       <c r="AK30" s="56"/>
@@ -9834,11 +9884,11 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>27.082608695652176</v>
+        <v>27.05</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9846,7 +9896,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>1.2097759596904467</v>
+        <v>1.1771672640382711</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -9949,7 +9999,9 @@
       <c r="AG31" s="98">
         <v>26.5</v>
       </c>
-      <c r="AH31" s="98"/>
+      <c r="AH31" s="98">
+        <v>29.2</v>
+      </c>
       <c r="AI31" s="98"/>
       <c r="AJ31" s="98"/>
       <c r="AK31" s="98"/>
@@ -9959,11 +10011,11 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>27.734782608695646</v>
+        <v>27.795833333333331</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9971,7 +10023,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.1402588333073567</v>
+        <v>1.2013095579450415</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10074,7 +10126,9 @@
       <c r="AG32" s="56">
         <v>19.533333333333331</v>
       </c>
-      <c r="AH32" s="56"/>
+      <c r="AH32" s="56">
+        <v>19.533333333333331</v>
+      </c>
       <c r="AI32" s="56"/>
       <c r="AJ32" s="56"/>
       <c r="AK32" s="56"/>
@@ -10084,11 +10138,11 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>19.720289855072455</v>
+        <v>19.712499999999991</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10096,7 +10150,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.4658519599718538</v>
+        <v>2.4580621048993905</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10197,9 +10251,11 @@
         <v>27.95</v>
       </c>
       <c r="AG33" s="56">
-        <v>27.933333333333341</v>
-      </c>
-      <c r="AH33" s="56"/>
+        <v>27.85</v>
+      </c>
+      <c r="AH33" s="56">
+        <v>27.05</v>
+      </c>
       <c r="AI33" s="56"/>
       <c r="AJ33" s="56"/>
       <c r="AK33" s="56"/>
@@ -10209,11 +10265,11 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>27.551449275362327</v>
+        <v>27.527083333333337</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10221,7 +10277,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.0714231121115461</v>
+        <v>1.0470571700825566</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10324,7 +10380,9 @@
       <c r="AG34" s="56">
         <v>21.2</v>
       </c>
-      <c r="AH34" s="56"/>
+      <c r="AH34" s="56">
+        <v>20.266666666666669</v>
+      </c>
       <c r="AI34" s="56"/>
       <c r="AJ34" s="56"/>
       <c r="AK34" s="56"/>
@@ -10334,11 +10392,11 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>20.637681159420286</v>
+        <v>20.622222222222216</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10346,7 +10404,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.1802197825818546</v>
+        <v>1.1647608453837854</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10447,9 +10505,11 @@
         <v>23.05</v>
       </c>
       <c r="AG35" s="56">
-        <v>25.666666666666671</v>
-      </c>
-      <c r="AH35" s="56"/>
+        <v>25.1</v>
+      </c>
+      <c r="AH35" s="56">
+        <v>23.75</v>
+      </c>
       <c r="AI35" s="56"/>
       <c r="AJ35" s="56"/>
       <c r="AK35" s="56"/>
@@ -10459,11 +10519,11 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.092028985507241</v>
+        <v>24.054166666666664</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10471,7 +10531,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.56711925385926065</v>
+        <v>0.52925693501868309</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10574,7 +10634,9 @@
       <c r="AG36" s="56">
         <v>20.25</v>
       </c>
-      <c r="AH36" s="56"/>
+      <c r="AH36" s="56">
+        <v>19.2</v>
+      </c>
       <c r="AI36" s="56"/>
       <c r="AJ36" s="56"/>
       <c r="AK36" s="56"/>
@@ -10584,11 +10646,11 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>19.086956521739136</v>
+        <v>19.091666666666672</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10596,7 +10658,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>1.1201075171762547</v>
+        <v>1.1248176621037906</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10699,7 +10761,9 @@
       <c r="AG37" s="56">
         <v>27.45</v>
       </c>
-      <c r="AH37" s="56"/>
+      <c r="AH37" s="56">
+        <v>26.95</v>
+      </c>
       <c r="AI37" s="56"/>
       <c r="AJ37" s="56"/>
       <c r="AK37" s="56"/>
@@ -10709,11 +10773,11 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>26.317391304347829</v>
+        <v>26.343750000000004</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10721,7 +10785,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>0.83298821253658772</v>
+        <v>0.85934690818876192</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10824,7 +10888,9 @@
       <c r="AG38" s="56">
         <v>17.5</v>
       </c>
-      <c r="AH38" s="56"/>
+      <c r="AH38" s="56">
+        <v>15.65</v>
+      </c>
       <c r="AI38" s="56"/>
       <c r="AJ38" s="56"/>
       <c r="AK38" s="56"/>
@@ -10834,11 +10900,11 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>15.3304347826087</v>
+        <v>15.343750000000002</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10846,7 +10912,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>0.56921208366632925</v>
+        <v>0.58252730105763106</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10949,7 +11015,9 @@
       <c r="AG39" s="56">
         <v>21.333333333333329</v>
       </c>
-      <c r="AH39" s="56"/>
+      <c r="AH39" s="56">
+        <v>20.266666666666669</v>
+      </c>
       <c r="AI39" s="56"/>
       <c r="AJ39" s="56"/>
       <c r="AK39" s="56"/>
@@ -10959,11 +11027,11 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>20.80869565217391</v>
+        <v>20.786111111111108</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11163,7 +11231,9 @@
       <c r="AG41" s="56">
         <v>19.8</v>
       </c>
-      <c r="AH41" s="56"/>
+      <c r="AH41" s="56">
+        <v>17.600000000000001</v>
+      </c>
       <c r="AI41" s="56"/>
       <c r="AJ41" s="56"/>
       <c r="AK41" s="56"/>
@@ -11173,11 +11243,11 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>18.609090909090909</v>
+        <v>18.565217391304351</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11185,7 +11255,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>0.79956497537320814</v>
+        <v>0.75569145758665002</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11286,7 +11356,9 @@
       <c r="AG42" s="56">
         <v>27.7</v>
       </c>
-      <c r="AH42" s="56"/>
+      <c r="AH42" s="56">
+        <v>25</v>
+      </c>
       <c r="AI42" s="56"/>
       <c r="AJ42" s="56"/>
       <c r="AK42" s="56"/>
@@ -11296,11 +11368,11 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>27.790909090909089</v>
+        <v>27.669565217391302</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11308,7 +11380,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.61687981970240813</v>
+        <v>0.49553594618462071</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11408,8 +11480,12 @@
       <c r="AF43" s="56">
         <v>28.35</v>
       </c>
-      <c r="AG43" s="56"/>
-      <c r="AH43" s="56"/>
+      <c r="AG43" s="56">
+        <v>29.05</v>
+      </c>
+      <c r="AH43" s="56">
+        <v>25.8</v>
+      </c>
       <c r="AI43" s="56"/>
       <c r="AJ43" s="56"/>
       <c r="AK43" s="56"/>
@@ -11419,11 +11495,11 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>28.547727272727272</v>
+        <v>28.454166666666662</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11534,7 +11610,9 @@
       <c r="AG44" s="56">
         <v>28.2</v>
       </c>
-      <c r="AH44" s="56"/>
+      <c r="AH44" s="56">
+        <v>26.45</v>
+      </c>
       <c r="AI44" s="56"/>
       <c r="AJ44" s="56"/>
       <c r="AK44" s="56"/>
@@ -11544,11 +11622,11 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>27.888043478260869</v>
+        <v>27.828125</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11556,7 +11634,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>0.65981859876513838</v>
+        <v>0.59990012050426955</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11659,7 +11737,9 @@
       <c r="AG45" s="56">
         <v>28.4</v>
       </c>
-      <c r="AH45" s="56"/>
+      <c r="AH45" s="56">
+        <v>25.55</v>
+      </c>
       <c r="AI45" s="56"/>
       <c r="AJ45" s="56"/>
       <c r="AK45" s="56"/>
@@ -11669,11 +11749,11 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>27.639130434782611</v>
+        <v>27.552083333333332</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11681,7 +11761,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>0.75029870412438271</v>
+        <v>0.66325160267510341</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12099,8 +12179,12 @@
       <c r="AF50" s="56">
         <v>29</v>
       </c>
-      <c r="AG50" s="56"/>
-      <c r="AH50" s="56"/>
+      <c r="AG50" s="56">
+        <v>28.55</v>
+      </c>
+      <c r="AH50" s="56">
+        <v>24.45</v>
+      </c>
       <c r="AI50" s="56"/>
       <c r="AJ50" s="56"/>
       <c r="AK50" s="56"/>
@@ -12110,11 +12194,11 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>28.145454545454548</v>
+        <v>28.008333333333336</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12122,7 +12206,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>0.9555549427519594</v>
+        <v>0.81843373063074765</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12383,7 +12467,9 @@
       <c r="AG53" s="56">
         <v>28.8</v>
       </c>
-      <c r="AH53" s="56"/>
+      <c r="AH53" s="56">
+        <v>24.45</v>
+      </c>
       <c r="AI53" s="56"/>
       <c r="AJ53" s="56"/>
       <c r="AK53" s="56"/>
@@ -12393,11 +12479,11 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>27.2</v>
+        <v>27.085416666666671</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12405,7 +12491,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>0.70132118141384936</v>
+        <v>0.58673784808052076</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12506,7 +12592,9 @@
         <v>29.2</v>
       </c>
       <c r="AG54" s="56"/>
-      <c r="AH54" s="56"/>
+      <c r="AH54" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AI54" s="56"/>
       <c r="AJ54" s="56"/>
       <c r="AK54" s="56"/>
@@ -12516,11 +12604,11 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>28.35</v>
+        <v>28.213043478260875</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12528,7 +12616,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>0.36072671469982254</v>
+        <v>0.22377019296069633</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12983,7 +13071,9 @@
       <c r="AG59" s="56">
         <v>29.6</v>
       </c>
-      <c r="AH59" s="56"/>
+      <c r="AH59" s="56">
+        <v>25.55</v>
+      </c>
       <c r="AI59" s="56"/>
       <c r="AJ59" s="56"/>
       <c r="AK59" s="56"/>
@@ -12993,11 +13083,11 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>28.2</v>
+        <v>28.089583333333334</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13005,7 +13095,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>0.98680990840986027</v>
+        <v>0.87639324174319455</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13217,7 +13307,9 @@
       <c r="AG61" s="56">
         <v>29.05</v>
       </c>
-      <c r="AH61" s="56"/>
+      <c r="AH61" s="56">
+        <v>28.15</v>
+      </c>
       <c r="AI61" s="56"/>
       <c r="AJ61" s="56"/>
       <c r="AK61" s="56"/>
@@ -13227,11 +13319,11 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>27.915942028985508</v>
+        <v>27.925694444444446</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13239,7 +13331,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>1.1111476900613795</v>
+        <v>1.1209001055203167</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13342,7 +13434,9 @@
       <c r="AG62" s="56">
         <v>28.666666666666671</v>
       </c>
-      <c r="AH62" s="56"/>
+      <c r="AH62" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AI62" s="56"/>
       <c r="AJ62" s="56"/>
       <c r="AK62" s="56"/>
@@ -13352,11 +13446,11 @@
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ62" s="71">
         <f t="shared" si="1"/>
-        <v>27.759420289855075</v>
+        <v>27.75277777777778</v>
       </c>
       <c r="AR62" s="71">
         <f>IFERROR(VLOOKUP(A62,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13364,7 +13458,7 @@
       </c>
       <c r="AS62" s="71">
         <f t="shared" si="2"/>
-        <v>1.8929154390384859</v>
+        <v>1.8862729269611904</v>
       </c>
     </row>
     <row r="63" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13625,7 +13719,9 @@
       <c r="AG65" s="56">
         <v>27.05</v>
       </c>
-      <c r="AH65" s="56"/>
+      <c r="AH65" s="56">
+        <v>27.35</v>
+      </c>
       <c r="AI65" s="56"/>
       <c r="AJ65" s="56"/>
       <c r="AK65" s="56"/>
@@ -13635,11 +13731,11 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>26.852173913043476</v>
+        <v>26.872916666666665</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13647,7 +13743,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.75458966518159443</v>
+        <v>0.77533241880478343</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13750,7 +13846,9 @@
       <c r="AG66" s="56">
         <v>27.8</v>
       </c>
-      <c r="AH66" s="56"/>
+      <c r="AH66" s="56">
+        <v>26.15</v>
+      </c>
       <c r="AI66" s="56"/>
       <c r="AJ66" s="56"/>
       <c r="AK66" s="56"/>
@@ -13760,11 +13858,11 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>27.119565217391294</v>
+        <v>27.079166666666655</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13772,7 +13870,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.93313229281474364</v>
+        <v>0.8927337420901047</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13871,7 +13969,9 @@
         <v>27.7</v>
       </c>
       <c r="AG67" s="56"/>
-      <c r="AH67" s="56"/>
+      <c r="AH67" s="56">
+        <v>27.05</v>
+      </c>
       <c r="AI67" s="56"/>
       <c r="AJ67" s="56"/>
       <c r="AK67" s="56"/>
@@ -13881,11 +13981,11 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>26.845238095238095</v>
+        <v>26.854545454545452</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13893,7 +13993,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.73413136621653408</v>
+        <v>0.74343872552389101</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13996,7 +14096,9 @@
       <c r="AG68" s="56">
         <v>27.45</v>
       </c>
-      <c r="AH68" s="56"/>
+      <c r="AH68" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AI68" s="56"/>
       <c r="AJ68" s="56"/>
       <c r="AK68" s="56"/>
@@ -14006,11 +14108,11 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>26.041304347826088</v>
+        <v>26.006250000000005</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14018,7 +14120,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>0.26025823961846939</v>
+        <v>0.2252038917923862</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14121,7 +14223,9 @@
       <c r="AG69" s="56">
         <v>26.5</v>
       </c>
-      <c r="AH69" s="56"/>
+      <c r="AH69" s="56">
+        <v>25.175000000000001</v>
+      </c>
       <c r="AI69" s="56"/>
       <c r="AJ69" s="56"/>
       <c r="AK69" s="56"/>
@@ -14131,11 +14235,11 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>25.984782608695649</v>
+        <v>25.951041666666665</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14143,7 +14247,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.25630199768611917</v>
+        <v>0.22256105565713469</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14240,7 +14344,9 @@
       <c r="AG70" s="56">
         <v>27.8</v>
       </c>
-      <c r="AH70" s="56"/>
+      <c r="AH70" s="56">
+        <v>27.13333333333334</v>
+      </c>
       <c r="AI70" s="56"/>
       <c r="AJ70" s="56"/>
       <c r="AK70" s="56"/>
@@ -14250,11 +14356,11 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v>27.478333333333332</v>
+        <v>27.461904761904758</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14262,7 +14368,7 @@
       </c>
       <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v>0.42390282755876285</v>
+        <v>0.40747425613018962</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14365,7 +14471,9 @@
       <c r="AG71" s="56">
         <v>27.033333333333331</v>
       </c>
-      <c r="AH71" s="56"/>
+      <c r="AH71" s="56">
+        <v>26.36666666666666</v>
+      </c>
       <c r="AI71" s="56"/>
       <c r="AJ71" s="56"/>
       <c r="AK71" s="56"/>
@@ -14375,11 +14483,11 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>27.355072463768114</v>
+        <v>27.313888888888886</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14387,7 +14495,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.42054563517898202</v>
+        <v>0.37936206029975494</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14488,7 +14596,9 @@
       <c r="AG72" s="56">
         <v>26.333333333333329</v>
       </c>
-      <c r="AH72" s="56"/>
+      <c r="AH72" s="56">
+        <v>27.9</v>
+      </c>
       <c r="AI72" s="56"/>
       <c r="AJ72" s="56"/>
       <c r="AK72" s="56"/>
@@ -14498,11 +14608,11 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>26.424242424242426</v>
+        <v>26.48840579710145</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14510,7 +14620,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.57973113797273612</v>
+        <v>0.64389451083176041</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14837,7 +14947,9 @@
       <c r="AG75" s="56">
         <v>16.333333333333329</v>
       </c>
-      <c r="AH75" s="56"/>
+      <c r="AH75" s="56">
+        <v>16.600000000000001</v>
+      </c>
       <c r="AI75" s="56"/>
       <c r="AJ75" s="56"/>
       <c r="AK75" s="56"/>
@@ -14847,11 +14959,11 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>16.59710144927536</v>
+        <v>16.597222222222221</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14859,7 +14971,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.75991190935147124</v>
+        <v>0.76003268229833232</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15087,7 +15199,9 @@
       <c r="AG77" s="56">
         <v>26.86666666666666</v>
       </c>
-      <c r="AH77" s="56"/>
+      <c r="AH77" s="56">
+        <v>24.2</v>
+      </c>
       <c r="AI77" s="56"/>
       <c r="AJ77" s="56"/>
       <c r="AK77" s="56"/>
@@ -15097,11 +15211,11 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>24.608695652173914</v>
+        <v>24.591666666666669</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15109,7 +15223,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.9084998088850327</v>
+        <v>1.8914708233777873</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15212,7 +15326,9 @@
       <c r="AG78" s="56">
         <v>33.35</v>
       </c>
-      <c r="AH78" s="56"/>
+      <c r="AH78" s="56">
+        <v>31.8</v>
+      </c>
       <c r="AI78" s="56"/>
       <c r="AJ78" s="56"/>
       <c r="AK78" s="56"/>
@@ -15222,11 +15338,11 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v>30.189130434782609</v>
+        <v>30.256249999999998</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15234,7 +15350,7 @@
       </c>
       <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v>1.8278764447735583</v>
+        <v>1.8949960099909475</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15337,7 +15453,9 @@
       <c r="AG79" s="56">
         <v>34.466666666666669</v>
       </c>
-      <c r="AH79" s="56"/>
+      <c r="AH79" s="56">
+        <v>32.533333333333331</v>
+      </c>
       <c r="AI79" s="56"/>
       <c r="AJ79" s="56"/>
       <c r="AK79" s="56"/>
@@ -15347,11 +15465,11 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v>31.286956521739135</v>
+        <v>31.338888888888892</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15359,7 +15477,7 @@
       </c>
       <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v>2.2522439549087458</v>
+        <v>2.3041763220585025</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15462,7 +15580,9 @@
       <c r="AG80" s="56">
         <v>23.466666666666669</v>
       </c>
-      <c r="AH80" s="56"/>
+      <c r="AH80" s="56">
+        <v>21.466666666666669</v>
+      </c>
       <c r="AI80" s="56"/>
       <c r="AJ80" s="56"/>
       <c r="AK80" s="56"/>
@@ -15472,11 +15592,11 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ80" s="71">
         <f t="shared" si="4"/>
-        <v>22.128985507246373</v>
+        <v>22.101388888888888</v>
       </c>
       <c r="AR80" s="71">
         <f>IFERROR(VLOOKUP(A80,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15484,7 +15604,7 @@
       </c>
       <c r="AS80" s="71">
         <f t="shared" si="5"/>
-        <v>1.7652964378410729</v>
+        <v>1.7376998194835878</v>
       </c>
     </row>
     <row r="81" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15702,7 +15822,9 @@
       <c r="AG82" s="56">
         <v>26</v>
       </c>
-      <c r="AH82" s="56"/>
+      <c r="AH82" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="AI82" s="56"/>
       <c r="AJ82" s="56"/>
       <c r="AK82" s="56"/>
@@ -15712,11 +15834,11 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ82" s="71">
         <f t="shared" si="4"/>
-        <v>27.516666666666673</v>
+        <v>27.479710144927541</v>
       </c>
       <c r="AR82" s="71">
         <f>IFERROR(VLOOKUP(A82,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15724,7 +15846,7 @@
       </c>
       <c r="AS82" s="71">
         <f t="shared" si="5"/>
-        <v>0.89549154670570275</v>
+        <v>0.85853502496657086</v>
       </c>
     </row>
     <row r="83" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15978,8 +16100,12 @@
       <c r="AF85" s="56">
         <v>29.65</v>
       </c>
-      <c r="AG85" s="56"/>
-      <c r="AH85" s="56"/>
+      <c r="AG85" s="56">
+        <v>31.45</v>
+      </c>
+      <c r="AH85" s="56">
+        <v>29.25</v>
+      </c>
       <c r="AI85" s="56"/>
       <c r="AJ85" s="56"/>
       <c r="AK85" s="56"/>
@@ -15989,11 +16115,11 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ85" s="71">
         <f t="shared" si="4"/>
-        <v>31.22000000000001</v>
+        <v>31.140909090909101</v>
       </c>
       <c r="AR85" s="71" t="str">
         <f>IFERROR(VLOOKUP(A85,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16104,7 +16230,9 @@
       <c r="AG86" s="56">
         <v>29.65</v>
       </c>
-      <c r="AH86" s="56"/>
+      <c r="AH86" s="56">
+        <v>29.35</v>
+      </c>
       <c r="AI86" s="56"/>
       <c r="AJ86" s="56"/>
       <c r="AK86" s="56"/>
@@ -16114,11 +16242,11 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>28.986956521739128</v>
+        <v>29.002083333333331</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16126,7 +16254,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>1.6072284304596387</v>
+        <v>1.6223552420538425</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16221,7 +16349,9 @@
       <c r="AG87" s="56">
         <v>29.8</v>
       </c>
-      <c r="AH87" s="56"/>
+      <c r="AH87" s="56">
+        <v>24.9</v>
+      </c>
       <c r="AI87" s="56"/>
       <c r="AJ87" s="56"/>
       <c r="AK87" s="56"/>
@@ -16231,11 +16361,11 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>28.694736842105261</v>
+        <v>28.504999999999995</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16243,7 +16373,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>0.9741541097401516</v>
+        <v>0.78441726763488617</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16346,7 +16476,9 @@
       <c r="AG88" s="56">
         <v>29.45</v>
       </c>
-      <c r="AH88" s="56"/>
+      <c r="AH88" s="56">
+        <v>27.05</v>
+      </c>
       <c r="AI88" s="56"/>
       <c r="AJ88" s="56"/>
       <c r="AK88" s="56"/>
@@ -16356,11 +16488,11 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>27.789130434782606</v>
+        <v>27.758333333333329</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16368,7 +16500,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>0.71935146226170588</v>
+        <v>0.68855436081242871</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16465,7 +16597,9 @@
       <c r="AG89" s="56">
         <v>29.4</v>
       </c>
-      <c r="AH89" s="56"/>
+      <c r="AH89" s="56">
+        <v>28.2</v>
+      </c>
       <c r="AI89" s="56"/>
       <c r="AJ89" s="56"/>
       <c r="AK89" s="56"/>
@@ -16475,11 +16609,11 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v>29.185000000000002</v>
+        <v>29.138095238095243</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16487,7 +16621,7 @@
       </c>
       <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v>1.4797906925047108</v>
+        <v>1.4328859305999515</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16584,7 +16718,9 @@
       <c r="AG90" s="56">
         <v>31</v>
       </c>
-      <c r="AH90" s="56"/>
+      <c r="AH90" s="56">
+        <v>29.3</v>
+      </c>
       <c r="AI90" s="56"/>
       <c r="AJ90" s="56"/>
       <c r="AK90" s="56"/>
@@ -16594,11 +16730,11 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v>29.699999999999996</v>
+        <v>29.680952380952373</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16606,7 +16742,7 @@
       </c>
       <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v>2.3703906078560451</v>
+        <v>2.3513429888084225</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16701,7 +16837,9 @@
       <c r="AG91" s="56">
         <v>29.6</v>
       </c>
-      <c r="AH91" s="56"/>
+      <c r="AH91" s="56">
+        <v>26.55</v>
+      </c>
       <c r="AI91" s="56"/>
       <c r="AJ91" s="56"/>
       <c r="AK91" s="56"/>
@@ -16711,11 +16849,11 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ91" s="71">
         <f t="shared" si="4"/>
-        <v>28.873684210526317</v>
+        <v>28.7575</v>
       </c>
       <c r="AR91" s="71" t="str">
         <f>IFERROR(VLOOKUP(A91,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16822,7 +16960,9 @@
       <c r="AG92" s="56">
         <v>18.8</v>
       </c>
-      <c r="AH92" s="56"/>
+      <c r="AH92" s="56">
+        <v>17.2</v>
+      </c>
       <c r="AI92" s="56"/>
       <c r="AJ92" s="56"/>
       <c r="AK92" s="56"/>
@@ -16832,11 +16972,11 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>16.75595238095238</v>
+        <v>16.776136363636365</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16844,7 +16984,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>0.87839363941517945</v>
+        <v>0.89857762209916459</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16947,7 +17087,9 @@
       <c r="AG93" s="56">
         <v>24.93333333333333</v>
       </c>
-      <c r="AH93" s="56"/>
+      <c r="AH93" s="56">
+        <v>22.333333333333329</v>
+      </c>
       <c r="AI93" s="56"/>
       <c r="AJ93" s="56"/>
       <c r="AK93" s="56"/>
@@ -16957,11 +17099,11 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>23.350724637681161</v>
+        <v>23.308333333333337</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16969,7 +17111,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.3608672405732918</v>
+        <v>1.3184759362254681</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17072,7 +17214,9 @@
       <c r="AG94" s="56">
         <v>18.149999999999999</v>
       </c>
-      <c r="AH94" s="56"/>
+      <c r="AH94" s="56">
+        <v>17.25</v>
+      </c>
       <c r="AI94" s="56"/>
       <c r="AJ94" s="56"/>
       <c r="AK94" s="56"/>
@@ -17082,11 +17226,11 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.136956521739126</v>
+        <v>17.141666666666662</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17094,7 +17238,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.0971095019384656</v>
+        <v>1.1018196468660015</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17197,7 +17341,9 @@
       <c r="AG95" s="56">
         <v>15.35</v>
       </c>
-      <c r="AH95" s="56"/>
+      <c r="AH95" s="56">
+        <v>15.65</v>
+      </c>
       <c r="AI95" s="56"/>
       <c r="AJ95" s="56"/>
       <c r="AK95" s="56"/>
@@ -17207,11 +17353,11 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>15.808695652173913</v>
+        <v>15.802083333333334</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17219,7 +17365,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>1.685444118195834</v>
+        <v>1.6788317993552546</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17401,7 +17547,9 @@
       <c r="AG97" s="56">
         <v>17.45</v>
       </c>
-      <c r="AH97" s="56"/>
+      <c r="AH97" s="56">
+        <v>17.899999999999999</v>
+      </c>
       <c r="AI97" s="56"/>
       <c r="AJ97" s="56"/>
       <c r="AK97" s="56"/>
@@ -17411,11 +17559,11 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ97" s="71">
         <f t="shared" si="4"/>
-        <v>17.028260869565219</v>
+        <v>17.064583333333335</v>
       </c>
       <c r="AR97" s="71">
         <f>IFERROR(VLOOKUP(A97,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17423,7 +17571,7 @@
       </c>
       <c r="AS97" s="71">
         <f t="shared" si="5"/>
-        <v>2.583660670784699</v>
+        <v>2.6199831345528146</v>
       </c>
     </row>
     <row r="98" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17526,7 +17674,9 @@
       <c r="AG98" s="56">
         <v>13.45</v>
       </c>
-      <c r="AH98" s="56"/>
+      <c r="AH98" s="56">
+        <v>13.3</v>
+      </c>
       <c r="AI98" s="56"/>
       <c r="AJ98" s="56"/>
       <c r="AK98" s="56"/>
@@ -17536,11 +17686,11 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>13.880434782608695</v>
+        <v>13.856250000000001</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17651,7 +17801,9 @@
       <c r="AG99" s="56">
         <v>15.266666666666669</v>
       </c>
-      <c r="AH99" s="56"/>
+      <c r="AH99" s="56">
+        <v>15.266666666666669</v>
+      </c>
       <c r="AI99" s="56"/>
       <c r="AJ99" s="56"/>
       <c r="AK99" s="56"/>
@@ -17661,11 +17813,11 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ99" s="71">
         <f t="shared" si="4"/>
-        <v>14.757971014492753</v>
+        <v>14.779166666666667</v>
       </c>
       <c r="AR99" s="71" t="str">
         <f>IFERROR(VLOOKUP(A99,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17889,7 +18041,9 @@
       <c r="AG101" s="56">
         <v>14.8</v>
       </c>
-      <c r="AH101" s="56"/>
+      <c r="AH101" s="56">
+        <v>13.8</v>
+      </c>
       <c r="AI101" s="56"/>
       <c r="AJ101" s="56"/>
       <c r="AK101" s="56"/>
@@ -17899,11 +18053,11 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ101" s="71">
         <f t="shared" si="4"/>
-        <v>14.571739130434782</v>
+        <v>14.539583333333333</v>
       </c>
       <c r="AR101" s="71">
         <f>IFERROR(VLOOKUP(A101,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17911,7 +18065,7 @@
       </c>
       <c r="AS101" s="71">
         <f t="shared" si="5"/>
-        <v>1.3237762953363514</v>
+        <v>1.2916204982349022</v>
       </c>
     </row>
     <row r="102" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18006,7 +18160,9 @@
       <c r="AG102" s="56">
         <v>15.866666666666671</v>
       </c>
-      <c r="AH102" s="56"/>
+      <c r="AH102" s="56">
+        <v>14.733333333333331</v>
+      </c>
       <c r="AI102" s="56"/>
       <c r="AJ102" s="56"/>
       <c r="AK102" s="56"/>
@@ -18016,11 +18172,11 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ102" s="71">
         <f t="shared" si="4"/>
-        <v>14.294736842105261</v>
+        <v>14.316666666666666</v>
       </c>
       <c r="AR102" s="71">
         <f>IFERROR(VLOOKUP(A102,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18028,7 +18184,7 @@
       </c>
       <c r="AS102" s="71">
         <f t="shared" si="5"/>
-        <v>2.5462739366697509</v>
+        <v>2.5682037612311568</v>
       </c>
     </row>
     <row r="103" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18174,7 +18330,9 @@
       <c r="AG104" s="56">
         <v>17.06666666666667</v>
       </c>
-      <c r="AH104" s="56"/>
+      <c r="AH104" s="56">
+        <v>16</v>
+      </c>
       <c r="AI104" s="56"/>
       <c r="AJ104" s="56"/>
       <c r="AK104" s="56"/>
@@ -18184,7 +18342,7 @@
       <c r="AO104" s="56"/>
       <c r="AP104" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ104" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18299,7 +18457,9 @@
       <c r="AG105" s="56">
         <v>18.866666666666671</v>
       </c>
-      <c r="AH105" s="56"/>
+      <c r="AH105" s="56">
+        <v>17.600000000000001</v>
+      </c>
       <c r="AI105" s="56"/>
       <c r="AJ105" s="56"/>
       <c r="AK105" s="56"/>
@@ -18309,11 +18469,11 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>18.707246376811597</v>
+        <v>18.661111111111115</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18321,7 +18481,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>1.613887238755968</v>
+        <v>1.5677519730554863</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18420,7 +18580,9 @@
       <c r="AG106" s="56">
         <v>15.6</v>
       </c>
-      <c r="AH106" s="56"/>
+      <c r="AH106" s="56">
+        <v>13.25</v>
+      </c>
       <c r="AI106" s="56"/>
       <c r="AJ106" s="56"/>
       <c r="AK106" s="56"/>
@@ -18430,11 +18592,11 @@
       <c r="AO106" s="56"/>
       <c r="AP106" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ106" s="71">
         <f t="shared" si="4"/>
-        <v>15.001190476190475</v>
+        <v>14.921590909090908</v>
       </c>
       <c r="AR106" s="71">
         <f>IFERROR(VLOOKUP(A106,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18442,7 +18604,7 @@
       </c>
       <c r="AS106" s="71">
         <f t="shared" si="5"/>
-        <v>0.93214218031794438</v>
+        <v>0.8525426132183771</v>
       </c>
     </row>
     <row r="107" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18624,7 +18786,9 @@
       <c r="AG108" s="56">
         <v>16.05</v>
       </c>
-      <c r="AH108" s="56"/>
+      <c r="AH108" s="56">
+        <v>14.75</v>
+      </c>
       <c r="AI108" s="56"/>
       <c r="AJ108" s="56"/>
       <c r="AK108" s="56"/>
@@ -18634,11 +18798,11 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>15.190217391304346</v>
+        <v>15.171874999999998</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18646,7 +18810,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>0.50799473213457524</v>
+        <v>0.48965234083022757</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18749,7 +18913,9 @@
       <c r="AG109" s="56">
         <v>15.55</v>
       </c>
-      <c r="AH109" s="56"/>
+      <c r="AH109" s="56">
+        <v>14.7</v>
+      </c>
       <c r="AI109" s="56"/>
       <c r="AJ109" s="56"/>
       <c r="AK109" s="56"/>
@@ -18759,11 +18925,11 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>15.769565217391303</v>
+        <v>15.725</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18771,7 +18937,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>1.1875164023447429</v>
+        <v>1.1429511849534393</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18870,7 +19036,9 @@
       <c r="AG110" s="56">
         <v>19.399999999999999</v>
       </c>
-      <c r="AH110" s="56"/>
+      <c r="AH110" s="56">
+        <v>16.666666666666671</v>
+      </c>
       <c r="AI110" s="56"/>
       <c r="AJ110" s="56"/>
       <c r="AK110" s="56"/>
@@ -18880,11 +19048,11 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>18.669841269841271</v>
+        <v>18.578787878787878</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18892,7 +19060,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.62318879241136926</v>
+        <v>0.53213540135797643</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18995,7 +19163,9 @@
       <c r="AG111" s="56">
         <v>17.2</v>
       </c>
-      <c r="AH111" s="56"/>
+      <c r="AH111" s="56">
+        <v>15.9</v>
+      </c>
       <c r="AI111" s="56"/>
       <c r="AJ111" s="56"/>
       <c r="AK111" s="56"/>
@@ -19005,11 +19175,11 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>16.895652173913039</v>
+        <v>16.854166666666661</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19017,7 +19187,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.53512717894584938</v>
+        <v>0.49364167169947137</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19116,7 +19286,9 @@
       <c r="AG112" s="56">
         <v>20.6</v>
       </c>
-      <c r="AH112" s="56"/>
+      <c r="AH112" s="56">
+        <v>18.533333333333331</v>
+      </c>
       <c r="AI112" s="56"/>
       <c r="AJ112" s="56"/>
       <c r="AK112" s="56"/>
@@ -19126,11 +19298,11 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>19.412698412698411</v>
+        <v>19.372727272727271</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19138,7 +19310,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.7782555702645126</v>
+        <v>1.7382844302933727</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19233,7 +19405,9 @@
         <v>20.06666666666667</v>
       </c>
       <c r="AG113" s="56"/>
-      <c r="AH113" s="56"/>
+      <c r="AH113" s="56">
+        <v>19.266666666666669</v>
+      </c>
       <c r="AI113" s="56"/>
       <c r="AJ113" s="56"/>
       <c r="AK113" s="56"/>
@@ -19243,11 +19417,11 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v>20.242105263157889</v>
+        <v>20.193333333333328</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19255,7 +19429,7 @@
       </c>
       <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v>1.2591142749346673</v>
+        <v>1.2103423451101065</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19338,7 +19512,9 @@
       </c>
       <c r="AF114" s="56"/>
       <c r="AG114" s="56"/>
-      <c r="AH114" s="56"/>
+      <c r="AH114" s="56">
+        <v>22.333333333333329</v>
+      </c>
       <c r="AI114" s="56"/>
       <c r="AJ114" s="56"/>
       <c r="AK114" s="56"/>
@@ -19348,7 +19524,7 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -19463,7 +19639,9 @@
       <c r="AG115" s="56">
         <v>28.9</v>
       </c>
-      <c r="AH115" s="56"/>
+      <c r="AH115" s="56">
+        <v>26.9</v>
+      </c>
       <c r="AI115" s="56"/>
       <c r="AJ115" s="56"/>
       <c r="AK115" s="56"/>
@@ -19473,11 +19651,11 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>27.85543478260869</v>
+        <v>27.815624999999994</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19485,7 +19663,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.37095897615710882</v>
+        <v>0.33114919354841277</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19588,7 +19766,9 @@
       <c r="AG116" s="56">
         <v>19.600000000000001</v>
       </c>
-      <c r="AH116" s="56"/>
+      <c r="AH116" s="56">
+        <v>19.666666666666671</v>
+      </c>
       <c r="AI116" s="56"/>
       <c r="AJ116" s="56"/>
       <c r="AK116" s="56"/>
@@ -19598,11 +19778,11 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>19.417391304347831</v>
+        <v>19.427777777777781</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19610,7 +19790,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>0.28595205624744224</v>
+        <v>0.29633852967739216</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19705,7 +19885,9 @@
       <c r="AG117" s="56">
         <v>28.8</v>
       </c>
-      <c r="AH117" s="56"/>
+      <c r="AH117" s="56">
+        <v>27.533333333333331</v>
+      </c>
       <c r="AI117" s="56"/>
       <c r="AJ117" s="56"/>
       <c r="AK117" s="56"/>
@@ -19715,11 +19897,11 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>27.771929824561401</v>
+        <v>27.759999999999998</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19727,7 +19909,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>1.1736197833786406</v>
+        <v>1.161689958817238</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19821,8 +20003,12 @@
       <c r="AF118" s="56">
         <v>30.06666666666667</v>
       </c>
-      <c r="AG118" s="56"/>
-      <c r="AH118" s="56"/>
+      <c r="AG118" s="56">
+        <v>30.333333333333329</v>
+      </c>
+      <c r="AH118" s="56">
+        <v>28.333333333333329</v>
+      </c>
       <c r="AI118" s="56"/>
       <c r="AJ118" s="56"/>
       <c r="AK118" s="56"/>
@@ -19832,11 +20018,11 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ118" s="71">
         <f t="shared" si="4"/>
-        <v>29.81754385964912</v>
+        <v>29.771428571428572</v>
       </c>
       <c r="AR118" s="71">
         <f>IFERROR(VLOOKUP(A118,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19844,7 +20030,7 @@
       </c>
       <c r="AS118" s="71">
         <f t="shared" si="5"/>
-        <v>2.8498556876061194</v>
+        <v>2.8037403993855712</v>
       </c>
     </row>
     <row r="119" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20242,7 +20428,9 @@
       <c r="AG122" s="56">
         <v>12.8</v>
       </c>
-      <c r="AH122" s="56"/>
+      <c r="AH122" s="56">
+        <v>12.93333333333333</v>
+      </c>
       <c r="AI122" s="56"/>
       <c r="AJ122" s="56"/>
       <c r="AK122" s="56"/>
@@ -20252,11 +20440,11 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>12.666666666666668</v>
+        <v>12.677777777777779</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20264,7 +20452,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>1.8103342385341374</v>
+        <v>1.8214453496452485</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21000,7 +21188,9 @@
       <c r="AG130" s="56">
         <v>16.36666666666666</v>
       </c>
-      <c r="AH130" s="56"/>
+      <c r="AH130" s="56">
+        <v>15.03333333333333</v>
+      </c>
       <c r="AI130" s="56"/>
       <c r="AJ130" s="56"/>
       <c r="AK130" s="56"/>
@@ -21010,11 +21200,11 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ130" s="71">
         <f t="shared" si="4"/>
-        <v>15.033333333333333</v>
+        <v>15.033333333333331</v>
       </c>
       <c r="AR130" s="71">
         <f>IFERROR(VLOOKUP(A130,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21022,7 +21212,7 @@
       </c>
       <c r="AS130" s="71">
         <f t="shared" si="5"/>
-        <v>1.1869432914879123</v>
+        <v>1.1869432914879106</v>
       </c>
     </row>
     <row r="131" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21123,7 +21313,9 @@
       <c r="AG131" s="56">
         <v>18.7</v>
       </c>
-      <c r="AH131" s="56"/>
+      <c r="AH131" s="56">
+        <v>19.899999999999999</v>
+      </c>
       <c r="AI131" s="56"/>
       <c r="AJ131" s="56"/>
       <c r="AK131" s="56"/>
@@ -21133,11 +21325,11 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>17.590909090909093</v>
+        <v>17.691304347826087</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21145,7 +21337,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.0391294990311337</v>
+        <v>1.139524755948127</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21327,7 +21519,9 @@
       <c r="AG133" s="56">
         <v>14.66666666666667</v>
       </c>
-      <c r="AH133" s="56"/>
+      <c r="AH133" s="56">
+        <v>15.366666666666671</v>
+      </c>
       <c r="AI133" s="56"/>
       <c r="AJ133" s="56"/>
       <c r="AK133" s="56"/>
@@ -21337,11 +21531,11 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>14.563768115942027</v>
+        <v>14.597222222222221</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21349,7 +21543,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>1.4255048119794775</v>
+        <v>1.4589589182596718</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21452,7 +21646,9 @@
       <c r="AG134" s="56">
         <v>18</v>
       </c>
-      <c r="AH134" s="56"/>
+      <c r="AH134" s="56">
+        <v>19.2</v>
+      </c>
       <c r="AI134" s="56"/>
       <c r="AJ134" s="56"/>
       <c r="AK134" s="56"/>
@@ -21462,11 +21658,11 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>18.217391304347828</v>
+        <v>18.258333333333336</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21474,7 +21670,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>2.093587041483449</v>
+        <v>2.1345290704689575</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21575,7 +21771,9 @@
       <c r="AG135" s="56">
         <v>19.55</v>
       </c>
-      <c r="AH135" s="56"/>
+      <c r="AH135" s="56">
+        <v>19</v>
+      </c>
       <c r="AI135" s="56"/>
       <c r="AJ135" s="56"/>
       <c r="AK135" s="56"/>
@@ -21585,11 +21783,11 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>18.645454545454541</v>
+        <v>18.660869565217389</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21597,7 +21795,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>0.84202893351153207</v>
+        <v>0.85744395327438028</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21902,7 +22100,9 @@
       <c r="AG138" s="56">
         <v>23.4</v>
       </c>
-      <c r="AH138" s="56"/>
+      <c r="AH138" s="56">
+        <v>22.733333333333331</v>
+      </c>
       <c r="AI138" s="56"/>
       <c r="AJ138" s="56"/>
       <c r="AK138" s="56"/>
@@ -21912,11 +22112,11 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>21.771014492753626</v>
+        <v>21.811111111111114</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21924,7 +22124,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>1.7754698021298942</v>
+        <v>1.8155664204873823</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22027,7 +22227,9 @@
       <c r="AG139" s="56">
         <v>15.75</v>
       </c>
-      <c r="AH139" s="56"/>
+      <c r="AH139" s="56">
+        <v>15.3</v>
+      </c>
       <c r="AI139" s="56"/>
       <c r="AJ139" s="56"/>
       <c r="AK139" s="56"/>
@@ -22037,11 +22239,11 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>14.592391304347826</v>
+        <v>14.621875000000001</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22049,7 +22251,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.3400930827788962</v>
+        <v>1.3695767784310711</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22152,7 +22354,9 @@
       <c r="AG140" s="56">
         <v>16.149999999999999</v>
       </c>
-      <c r="AH140" s="56"/>
+      <c r="AH140" s="56">
+        <v>17.100000000000001</v>
+      </c>
       <c r="AI140" s="56"/>
       <c r="AJ140" s="56"/>
       <c r="AK140" s="56"/>
@@ -22162,11 +22366,11 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.197826086956521</v>
+        <v>16.235416666666669</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22174,7 +22378,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.47989199351937195</v>
+        <v>0.51748257322952007</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22277,7 +22481,9 @@
       <c r="AG141" s="56">
         <v>14.066666666666659</v>
       </c>
-      <c r="AH141" s="56"/>
+      <c r="AH141" s="56">
+        <v>15.53333333333333</v>
+      </c>
       <c r="AI141" s="56"/>
       <c r="AJ141" s="56"/>
       <c r="AK141" s="56"/>
@@ -22287,11 +22493,11 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>14.284057971014494</v>
+        <v>14.33611111111111</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22299,7 +22505,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.5233730653921835</v>
+        <v>1.5754262054887995</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22402,7 +22608,9 @@
       <c r="AG142" s="56">
         <v>13.675000000000001</v>
       </c>
-      <c r="AH142" s="56"/>
+      <c r="AH142" s="56">
+        <v>13.4</v>
+      </c>
       <c r="AI142" s="56"/>
       <c r="AJ142" s="56"/>
       <c r="AK142" s="56"/>
@@ -22412,11 +22620,11 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>12.542391304347827</v>
+        <v>12.578125</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22424,7 +22632,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>1.3492317109068068</v>
+        <v>1.3849654065589796</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22633,7 +22841,9 @@
       <c r="AF144" s="56">
         <v>16.666666666666671</v>
       </c>
-      <c r="AG144" s="56"/>
+      <c r="AG144" s="56">
+        <v>17.399999999999999</v>
+      </c>
       <c r="AH144" s="56"/>
       <c r="AI144" s="56"/>
       <c r="AJ144" s="56"/>
@@ -22644,11 +22854,11 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ144" s="71">
         <f t="shared" si="7"/>
-        <v>16.884848484848487</v>
+        <v>16.907246376811596</v>
       </c>
       <c r="AR144" s="71">
         <f>IFERROR(VLOOKUP(A144,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22656,7 +22866,7 @@
       </c>
       <c r="AS144" s="71">
         <f t="shared" si="8"/>
-        <v>1.1957749592893467</v>
+        <v>1.2181728512524561</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22759,7 +22969,9 @@
       <c r="AG145" s="56">
         <v>22.533333333333331</v>
       </c>
-      <c r="AH145" s="56"/>
+      <c r="AH145" s="56">
+        <v>21.666666666666671</v>
+      </c>
       <c r="AI145" s="56"/>
       <c r="AJ145" s="56"/>
       <c r="AK145" s="56"/>
@@ -22769,11 +22981,11 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>20.675362318840577</v>
+        <v>20.716666666666665</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22781,7 +22993,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>1.2553665511714378</v>
+        <v>1.296670898997526</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23007,7 +23219,9 @@
       <c r="AG147" s="56">
         <v>26.666666666666671</v>
       </c>
-      <c r="AH147" s="56"/>
+      <c r="AH147" s="56">
+        <v>25.266666666666669</v>
+      </c>
       <c r="AI147" s="56"/>
       <c r="AJ147" s="56"/>
       <c r="AK147" s="56"/>
@@ -23017,11 +23231,11 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>25.715942028985509</v>
+        <v>25.697222222222223</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23029,7 +23243,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>2.2800629700543809</v>
+        <v>2.2613431632910945</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23123,14 +23337,18 @@
       <c r="AD148" s="56">
         <v>30.333333333333329</v>
       </c>
-      <c r="AE148" s="56"/>
+      <c r="AE148" s="56">
+        <v>29.8</v>
+      </c>
       <c r="AF148" s="56">
-        <v>29.6</v>
+        <v>29.13333333333334</v>
       </c>
       <c r="AG148" s="56">
         <v>30.06666666666667</v>
       </c>
-      <c r="AH148" s="56"/>
+      <c r="AH148" s="56">
+        <v>32.333333333333343</v>
+      </c>
       <c r="AI148" s="56"/>
       <c r="AJ148" s="56"/>
       <c r="AK148" s="56"/>
@@ -23140,11 +23358,11 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>29.769696969696973</v>
+        <v>29.858333333333334</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23152,7 +23370,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.4999046027809442</v>
+        <v>1.5885409664173054</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23688,7 +23906,9 @@
       </c>
       <c r="AF154" s="56"/>
       <c r="AG154" s="56"/>
-      <c r="AH154" s="56"/>
+      <c r="AH154" s="56">
+        <v>20.350000000000001</v>
+      </c>
       <c r="AI154" s="56"/>
       <c r="AJ154" s="56"/>
       <c r="AK154" s="56"/>
@@ -23698,11 +23918,11 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ154" s="71">
         <f t="shared" si="7"/>
-        <v>20.00714285714286</v>
+        <v>20.022727272727277</v>
       </c>
       <c r="AR154" s="71">
         <f>IFERROR(VLOOKUP(A154,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23710,7 +23930,7 @@
       </c>
       <c r="AS154" s="71">
         <f t="shared" si="8"/>
-        <v>0.74168741282201012</v>
+        <v>0.75727182840642726</v>
       </c>
     </row>
     <row r="155" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23813,7 +24033,9 @@
       <c r="AG155" s="56">
         <v>29.333333333333329</v>
       </c>
-      <c r="AH155" s="56"/>
+      <c r="AH155" s="56">
+        <v>25.866666666666671</v>
+      </c>
       <c r="AI155" s="56"/>
       <c r="AJ155" s="56"/>
       <c r="AK155" s="56"/>
@@ -23823,11 +24045,11 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>27.594202898550733</v>
+        <v>27.522222222222229</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23835,7 +24057,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>0.26683875595061224</v>
+        <v>0.19485807962210799</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24004,8 +24226,12 @@
       <c r="AF157" s="56">
         <v>27.066666666666659</v>
       </c>
-      <c r="AG157" s="56"/>
-      <c r="AH157" s="56"/>
+      <c r="AG157" s="56">
+        <v>28.8</v>
+      </c>
+      <c r="AH157" s="56">
+        <v>26.4</v>
+      </c>
       <c r="AI157" s="56"/>
       <c r="AJ157" s="56"/>
       <c r="AK157" s="56"/>
@@ -24015,11 +24241,11 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ157" s="71">
         <f t="shared" si="7"/>
-        <v>27.666666666666661</v>
+        <v>27.659649122807014</v>
       </c>
       <c r="AR157" s="71">
         <f>IFERROR(VLOOKUP(A157,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24027,7 +24253,7 @@
       </c>
       <c r="AS157" s="71">
         <f t="shared" si="8"/>
-        <v>0.68246173796103093</v>
+        <v>0.67544419410138445</v>
       </c>
     </row>
     <row r="158" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24122,7 +24348,9 @@
       <c r="AG158" s="56">
         <v>30.06666666666667</v>
       </c>
-      <c r="AH158" s="56"/>
+      <c r="AH158" s="56">
+        <v>27.933333333333341</v>
+      </c>
       <c r="AI158" s="56"/>
       <c r="AJ158" s="56"/>
       <c r="AK158" s="56"/>
@@ -24132,11 +24360,11 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>29.175438596491237</v>
+        <v>29.113333333333344</v>
       </c>
       <c r="AR158" s="71">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24144,7 +24372,7 @@
       </c>
       <c r="AS158" s="71">
         <f t="shared" si="8"/>
-        <v>1.8924861508249577</v>
+        <v>1.8303808876670651</v>
       </c>
     </row>
     <row r="159" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24247,7 +24475,9 @@
       <c r="AG159" s="56">
         <v>20.8</v>
       </c>
-      <c r="AH159" s="56"/>
+      <c r="AH159" s="56">
+        <v>18.600000000000001</v>
+      </c>
       <c r="AI159" s="56"/>
       <c r="AJ159" s="56"/>
       <c r="AK159" s="56"/>
@@ -24257,11 +24487,11 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>20.286956521739132</v>
+        <v>20.216666666666669</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24269,7 +24499,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>1.7797481632268521</v>
+        <v>1.7094583081543888</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24367,8 +24597,12 @@
       <c r="AF160" s="56">
         <v>27.266666666666669</v>
       </c>
-      <c r="AG160" s="56"/>
-      <c r="AH160" s="56"/>
+      <c r="AG160" s="56">
+        <v>28.86666666666666</v>
+      </c>
+      <c r="AH160" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AI160" s="56"/>
       <c r="AJ160" s="56"/>
       <c r="AK160" s="56"/>
@@ -24378,11 +24612,11 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>26.914285714285718</v>
+        <v>27.020289855072466</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24570,7 +24804,9 @@
       <c r="AG162" s="56">
         <v>29.133333333333329</v>
       </c>
-      <c r="AH162" s="56"/>
+      <c r="AH162" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="AI162" s="56"/>
       <c r="AJ162" s="56"/>
       <c r="AK162" s="56"/>
@@ -24580,11 +24816,11 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>28.087878787878779</v>
+        <v>28.026086956521731</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24592,7 +24828,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>0.2476771689724302</v>
+        <v>0.18588533761538173</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24695,7 +24931,9 @@
       <c r="AG163" s="56">
         <v>21.6</v>
       </c>
-      <c r="AH163" s="56"/>
+      <c r="AH163" s="56">
+        <v>20.666666666666671</v>
+      </c>
       <c r="AI163" s="56"/>
       <c r="AJ163" s="56"/>
       <c r="AK163" s="56"/>
@@ -24705,11 +24943,11 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.205797101449281</v>
+        <v>21.183333333333341</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24717,7 +24955,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>5.5482847553133041E-2</v>
+        <v>3.3019079437192289E-2</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24820,7 +25058,9 @@
       <c r="AG164" s="56">
         <v>24.9</v>
       </c>
-      <c r="AH164" s="56"/>
+      <c r="AH164" s="56">
+        <v>24.1</v>
+      </c>
       <c r="AI164" s="56"/>
       <c r="AJ164" s="56"/>
       <c r="AK164" s="56"/>
@@ -24830,11 +25070,11 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>24.858695652173914</v>
+        <v>24.827083333333334</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24842,7 +25082,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.0463649925092433</v>
+        <v>1.0147526736686636</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25024,7 +25264,9 @@
       <c r="AG166" s="56">
         <v>16.333333333333329</v>
       </c>
-      <c r="AH166" s="56"/>
+      <c r="AH166" s="56">
+        <v>16.06666666666667</v>
+      </c>
       <c r="AI166" s="56"/>
       <c r="AJ166" s="56"/>
       <c r="AK166" s="56"/>
@@ -25034,11 +25276,11 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>14.736231884057968</v>
+        <v>14.791666666666664</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25046,7 +25288,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>1.2890691106060181</v>
+        <v>1.3445038932147142</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25149,7 +25391,9 @@
       <c r="AG167" s="56">
         <v>20.733333333333331</v>
       </c>
-      <c r="AH167" s="56"/>
+      <c r="AH167" s="56">
+        <v>19.8</v>
+      </c>
       <c r="AI167" s="56"/>
       <c r="AJ167" s="56"/>
       <c r="AK167" s="56"/>
@@ -25159,11 +25403,11 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>20.078260869565216</v>
+        <v>20.066666666666666</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25171,7 +25415,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>1.3932087014601073</v>
+        <v>1.3816144985615573</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25274,7 +25518,9 @@
       <c r="AG168" s="56">
         <v>29</v>
       </c>
-      <c r="AH168" s="56"/>
+      <c r="AH168" s="56">
+        <v>24.9</v>
+      </c>
       <c r="AI168" s="56"/>
       <c r="AJ168" s="56"/>
       <c r="AK168" s="56"/>
@@ -25284,11 +25530,11 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>27.202173913043477</v>
+        <v>27.106249999999999</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25296,7 +25542,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>1.5169056314995473</v>
+        <v>1.4209817184560691</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25399,7 +25645,9 @@
       <c r="AG169" s="56">
         <v>11.3</v>
       </c>
-      <c r="AH169" s="56"/>
+      <c r="AH169" s="56">
+        <v>10.75</v>
+      </c>
       <c r="AI169" s="56"/>
       <c r="AJ169" s="56"/>
       <c r="AK169" s="56"/>
@@ -25409,11 +25657,11 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>10.430434782608696</v>
+        <v>10.44375</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25421,7 +25669,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>1.2520619346735042</v>
+        <v>1.2653771520648078</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25516,7 +25764,9 @@
       <c r="AG170" s="56">
         <v>24.333333333333329</v>
       </c>
-      <c r="AH170" s="56"/>
+      <c r="AH170" s="56">
+        <v>24.466666666666669</v>
+      </c>
       <c r="AI170" s="56"/>
       <c r="AJ170" s="56"/>
       <c r="AK170" s="56"/>
@@ -25526,11 +25776,11 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ170" s="71">
         <f t="shared" si="7"/>
-        <v>26.147368421052629</v>
+        <v>26.063333333333333</v>
       </c>
       <c r="AR170" s="71">
         <f>IFERROR(VLOOKUP(A170,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25538,7 +25788,7 @@
       </c>
       <c r="AS170" s="71">
         <f t="shared" si="8"/>
-        <v>0.9750503640253001</v>
+        <v>0.8910152763060033</v>
       </c>
     </row>
     <row r="171" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25758,7 +26008,9 @@
       <c r="AG172" s="56">
         <v>26.3</v>
       </c>
-      <c r="AH172" s="56"/>
+      <c r="AH172" s="56">
+        <v>25.1</v>
+      </c>
       <c r="AI172" s="56"/>
       <c r="AJ172" s="56"/>
       <c r="AK172" s="56"/>
@@ -25768,11 +26020,11 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>25.013043478260872</v>
+        <v>25.016666666666669</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25780,7 +26032,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>0.96278084120918095</v>
+        <v>0.96640402961497784</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25883,7 +26135,9 @@
       <c r="AG173" s="56">
         <v>25.35</v>
       </c>
-      <c r="AH173" s="56"/>
+      <c r="AH173" s="56">
+        <v>24.9</v>
+      </c>
       <c r="AI173" s="56"/>
       <c r="AJ173" s="56"/>
       <c r="AK173" s="56"/>
@@ -25893,11 +26147,11 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>23.843478260869563</v>
+        <v>23.887499999999999</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25905,7 +26159,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>0.34562503099012432</v>
+        <v>0.38964677012056015</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26488,8 +26742,12 @@
       <c r="AF179" s="56">
         <v>18.7</v>
       </c>
-      <c r="AG179" s="56"/>
-      <c r="AH179" s="56"/>
+      <c r="AG179" s="56">
+        <v>18.8</v>
+      </c>
+      <c r="AH179" s="56">
+        <v>17.649999999999999</v>
+      </c>
       <c r="AI179" s="56"/>
       <c r="AJ179" s="56"/>
       <c r="AK179" s="56"/>
@@ -26499,11 +26757,11 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>17.663636363636364</v>
+        <v>17.710416666666667</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26511,7 +26769,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>0.89868950481519505</v>
+        <v>0.94546980784549817</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26970,7 +27228,9 @@
       <c r="AG184" s="56">
         <v>30</v>
       </c>
-      <c r="AH184" s="56"/>
+      <c r="AH184" s="56">
+        <v>29.466666666666669</v>
+      </c>
       <c r="AI184" s="56"/>
       <c r="AJ184" s="56"/>
       <c r="AK184" s="56"/>
@@ -26980,11 +27240,11 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ184" s="71">
         <f t="shared" si="7"/>
-        <v>27.536231884057976</v>
+        <v>27.616666666666674</v>
       </c>
       <c r="AR184" s="71">
         <f>IFERROR(VLOOKUP(A184,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26992,7 +27252,7 @@
       </c>
       <c r="AS184" s="71">
         <f t="shared" si="8"/>
-        <v>1.3702176849954064</v>
+        <v>1.4506524676041046</v>
       </c>
     </row>
     <row r="185" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27093,7 +27353,9 @@
       <c r="AG185" s="56">
         <v>30.133333333333329</v>
       </c>
-      <c r="AH185" s="56"/>
+      <c r="AH185" s="56">
+        <v>29.8</v>
+      </c>
       <c r="AI185" s="56"/>
       <c r="AJ185" s="56"/>
       <c r="AK185" s="56"/>
@@ -27103,11 +27365,11 @@
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ185" s="71">
         <f t="shared" si="7"/>
-        <v>27.706060606060603</v>
+        <v>27.79710144927536</v>
       </c>
       <c r="AR185" s="71">
         <f>IFERROR(VLOOKUP(A185,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27115,7 +27377,7 @@
       </c>
       <c r="AS185" s="71">
         <f t="shared" si="8"/>
-        <v>0.39205256535763411</v>
+        <v>0.48309340857239036</v>
       </c>
     </row>
     <row r="186" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27376,7 +27638,9 @@
       <c r="AG188" s="56">
         <v>17.866666666666671</v>
       </c>
-      <c r="AH188" s="56"/>
+      <c r="AH188" s="56">
+        <v>17.466666666666669</v>
+      </c>
       <c r="AI188" s="56"/>
       <c r="AJ188" s="56"/>
       <c r="AK188" s="56"/>
@@ -27386,11 +27650,11 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>16.820289855072463</v>
+        <v>16.847222222222225</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27398,7 +27662,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.187608662550744</v>
+        <v>1.2145410297005057</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27485,7 +27749,9 @@
       <c r="AG189" s="56">
         <v>31.6</v>
       </c>
-      <c r="AH189" s="56"/>
+      <c r="AH189" s="56">
+        <v>28.4</v>
+      </c>
       <c r="AI189" s="56"/>
       <c r="AJ189" s="56"/>
       <c r="AK189" s="56"/>
@@ -27495,11 +27761,11 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ189" s="71">
         <f t="shared" si="7"/>
-        <v>28.724444444444444</v>
+        <v>28.704166666666666</v>
       </c>
       <c r="AR189" s="71">
         <f>IFERROR(VLOOKUP(A189,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27507,7 +27773,7 @@
       </c>
       <c r="AS189" s="71">
         <f t="shared" si="8"/>
-        <v>0.58290845417212367</v>
+        <v>0.56263067639434539</v>
       </c>
     </row>
     <row r="190" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27610,7 +27876,9 @@
       <c r="AG190" s="56">
         <v>30.333333333333329</v>
       </c>
-      <c r="AH190" s="56"/>
+      <c r="AH190" s="56">
+        <v>28.933333333333341</v>
+      </c>
       <c r="AI190" s="56"/>
       <c r="AJ190" s="56"/>
       <c r="AK190" s="56"/>
@@ -27620,11 +27888,11 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>28.173913043478262</v>
+        <v>28.205555555555559</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27632,7 +27900,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>0.15192915417516062</v>
+        <v>0.18357166625245824</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27729,7 +27997,9 @@
       <c r="AG191" s="56">
         <v>19.350000000000001</v>
       </c>
-      <c r="AH191" s="56"/>
+      <c r="AH191" s="56">
+        <v>18.2</v>
+      </c>
       <c r="AI191" s="56"/>
       <c r="AJ191" s="56"/>
       <c r="AK191" s="56"/>
@@ -27739,11 +28009,11 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>18.245000000000001</v>
+        <v>18.242857142857144</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27751,7 +28021,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>1.2132769950150504</v>
+        <v>1.2111341378721932</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27854,7 +28124,9 @@
       <c r="AG192" s="56">
         <v>27.2</v>
       </c>
-      <c r="AH192" s="56"/>
+      <c r="AH192" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AI192" s="56"/>
       <c r="AJ192" s="56"/>
       <c r="AK192" s="56"/>
@@ -27864,11 +28136,11 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>25.550724637681164</v>
+        <v>25.62777777777778</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27876,7 +28148,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>1.0785348217215436</v>
+        <v>1.1555879618181599</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27977,7 +28249,9 @@
       <c r="AG193" s="56">
         <v>28.75</v>
       </c>
-      <c r="AH193" s="56"/>
+      <c r="AH193" s="56">
+        <v>28.75</v>
+      </c>
       <c r="AI193" s="56"/>
       <c r="AJ193" s="56"/>
       <c r="AK193" s="56"/>
@@ -27987,11 +28261,11 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ193" s="71">
         <f t="shared" si="7"/>
-        <v>26.911363636363639</v>
+        <v>26.991304347826091</v>
       </c>
       <c r="AR193" s="71">
         <f>IFERROR(VLOOKUP(A193,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27999,7 +28273,7 @@
       </c>
       <c r="AS193" s="71">
         <f t="shared" si="8"/>
-        <v>1.0000458429306178</v>
+        <v>1.07998655439307</v>
       </c>
     </row>
     <row r="194" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28102,7 +28376,9 @@
       <c r="AG194" s="56">
         <v>22.266666666666669</v>
       </c>
-      <c r="AH194" s="56"/>
+      <c r="AH194" s="56">
+        <v>22.6</v>
+      </c>
       <c r="AI194" s="56"/>
       <c r="AJ194" s="56"/>
       <c r="AK194" s="56"/>
@@ -28112,11 +28388,11 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>21.252173913043475</v>
+        <v>21.308333333333334</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28124,7 +28400,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>4.0063540856195345E-2</v>
+        <v>9.6222961146054331E-2</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28219,7 +28495,9 @@
       <c r="AG195" s="56">
         <v>28.86666666666666</v>
       </c>
-      <c r="AH195" s="56"/>
+      <c r="AH195" s="56">
+        <v>24.666666666666671</v>
+      </c>
       <c r="AI195" s="56"/>
       <c r="AJ195" s="56"/>
       <c r="AK195" s="56"/>
@@ -28229,11 +28507,11 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>25.79649122807017</v>
+        <v>25.739999999999991</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28241,7 +28519,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>1.1326706274992588</v>
+        <v>1.0761793994290798</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28336,7 +28614,9 @@
       <c r="AG196" s="56">
         <v>23.666666666666671</v>
       </c>
-      <c r="AH196" s="56"/>
+      <c r="AH196" s="56">
+        <v>20</v>
+      </c>
       <c r="AI196" s="56"/>
       <c r="AJ196" s="56"/>
       <c r="AK196" s="56"/>
@@ -28346,11 +28626,11 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>20.64385964912281</v>
+        <v>20.611666666666672</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28358,7 +28638,7 @@
       </c>
       <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v>1.34365434858314</v>
+        <v>1.311461366127002</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28461,7 +28741,9 @@
       <c r="AG197" s="56">
         <v>26.06666666666667</v>
       </c>
-      <c r="AH197" s="56"/>
+      <c r="AH197" s="56">
+        <v>26.6</v>
+      </c>
       <c r="AI197" s="56"/>
       <c r="AJ197" s="56"/>
       <c r="AK197" s="56"/>
@@ -28470,20 +28752,20 @@
       <c r="AN197" s="56"/>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
-        <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>23</v>
+        <f t="shared" ref="AP197:AP212" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
+        <v>24</v>
       </c>
       <c r="AQ197" s="71">
-        <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>25.611594202898548</v>
+        <f t="shared" ref="AQ197:AQ212" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
+        <v>25.652777777777775</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.067391244533901</v>
       </c>
       <c r="AS197" s="71">
-        <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>1.5442029583646466</v>
+        <f t="shared" ref="AS197:AS212" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
+        <v>1.5853865332438737</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28586,7 +28868,9 @@
       <c r="AG198" s="56">
         <v>23.35</v>
       </c>
-      <c r="AH198" s="56"/>
+      <c r="AH198" s="56">
+        <v>21.8</v>
+      </c>
       <c r="AI198" s="56"/>
       <c r="AJ198" s="56"/>
       <c r="AK198" s="56"/>
@@ -28596,11 +28880,11 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>21.791304347826088</v>
+        <v>21.791666666666668</v>
       </c>
       <c r="AR198" s="71" t="str">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28711,7 +28995,9 @@
       <c r="AG199" s="56">
         <v>17.06666666666667</v>
       </c>
-      <c r="AH199" s="56"/>
+      <c r="AH199" s="56">
+        <v>17.533333333333331</v>
+      </c>
       <c r="AI199" s="56"/>
       <c r="AJ199" s="56"/>
       <c r="AK199" s="56"/>
@@ -28721,11 +29007,11 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>16.649275362318836</v>
+        <v>16.686111111111106</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28733,7 +29019,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>0.65770254025769503</v>
+        <v>0.69453828904996584</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28834,7 +29120,9 @@
       <c r="AG200" s="56">
         <v>15.6</v>
       </c>
-      <c r="AH200" s="56"/>
+      <c r="AH200" s="56">
+        <v>15.4</v>
+      </c>
       <c r="AI200" s="56"/>
       <c r="AJ200" s="56"/>
       <c r="AK200" s="56"/>
@@ -28844,11 +29132,11 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>14.886363636363638</v>
+        <v>14.908695652173915</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28856,7 +29144,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>1.5067199423298892</v>
+        <v>1.5290519581401654</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28959,7 +29247,9 @@
       <c r="AG201" s="56">
         <v>28.25</v>
       </c>
-      <c r="AH201" s="56"/>
+      <c r="AH201" s="56">
+        <v>26.35</v>
+      </c>
       <c r="AI201" s="56"/>
       <c r="AJ201" s="56"/>
       <c r="AK201" s="56"/>
@@ -28969,11 +29259,11 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ201" s="71">
         <f t="shared" si="10"/>
-        <v>26.495652173913044</v>
+        <v>26.489583333333332</v>
       </c>
       <c r="AR201" s="71">
         <f>IFERROR(VLOOKUP(A201,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28981,7 +29271,7 @@
       </c>
       <c r="AS201" s="71">
         <f t="shared" si="11"/>
-        <v>1.0854158508445728</v>
+        <v>1.0793470102648612</v>
       </c>
     </row>
     <row r="202" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29078,7 +29368,9 @@
       <c r="AG202" s="56">
         <v>14</v>
       </c>
-      <c r="AH202" s="56"/>
+      <c r="AH202" s="56">
+        <v>13.15</v>
+      </c>
       <c r="AI202" s="56"/>
       <c r="AJ202" s="56"/>
       <c r="AK202" s="56"/>
@@ -29088,11 +29380,11 @@
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ202" s="71">
         <f t="shared" si="10"/>
-        <v>13.954999999999998</v>
+        <v>13.916666666666664</v>
       </c>
       <c r="AR202" s="71">
         <f>IFERROR(VLOOKUP(A202,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29100,7 +29392,7 @@
       </c>
       <c r="AS202" s="71">
         <f t="shared" si="11"/>
-        <v>0.63331452033683888</v>
+        <v>0.59498118700350489</v>
       </c>
     </row>
     <row r="203" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29203,7 +29495,9 @@
       <c r="AG203" s="56">
         <v>15.2</v>
       </c>
-      <c r="AH203" s="56"/>
+      <c r="AH203" s="56">
+        <v>13.933333333333341</v>
+      </c>
       <c r="AI203" s="56"/>
       <c r="AJ203" s="56"/>
       <c r="AK203" s="56"/>
@@ -29213,11 +29507,11 @@
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ203" s="71">
         <f t="shared" si="10"/>
-        <v>14.6695652173913</v>
+        <v>14.638888888888886</v>
       </c>
       <c r="AR203" s="71">
         <f>IFERROR(VLOOKUP(A203,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29225,7 +29519,7 @@
       </c>
       <c r="AS203" s="71">
         <f t="shared" si="11"/>
-        <v>2.3219590571671098</v>
+        <v>2.2912827286646955</v>
       </c>
     </row>
     <row r="204" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29401,9 +29695,15 @@
       <c r="AE205" s="56">
         <v>14.525</v>
       </c>
-      <c r="AF205" s="56"/>
-      <c r="AG205" s="56"/>
-      <c r="AH205" s="56"/>
+      <c r="AF205" s="56">
+        <v>15.5</v>
+      </c>
+      <c r="AG205" s="56">
+        <v>14.75</v>
+      </c>
+      <c r="AH205" s="56">
+        <v>15.074999999999999</v>
+      </c>
       <c r="AI205" s="56"/>
       <c r="AJ205" s="56"/>
       <c r="AK205" s="56"/>
@@ -29413,11 +29713,11 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ205" s="71">
         <f t="shared" si="10"/>
-        <v>15.444047619047621</v>
+        <v>15.402083333333335</v>
       </c>
       <c r="AR205" s="71">
         <f>IFERROR(VLOOKUP(A205,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29425,7 +29725,7 @@
       </c>
       <c r="AS205" s="71">
         <f t="shared" si="11"/>
-        <v>1.1974984936967008</v>
+        <v>1.1555342079824147</v>
       </c>
     </row>
     <row r="206" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29525,7 +29825,9 @@
       <c r="AF206" s="56">
         <v>15.4</v>
       </c>
-      <c r="AG206" s="56"/>
+      <c r="AG206" s="56">
+        <v>15</v>
+      </c>
       <c r="AH206" s="56"/>
       <c r="AI206" s="56"/>
       <c r="AJ206" s="56"/>
@@ -29536,11 +29838,11 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ206" s="71">
         <f t="shared" si="10"/>
-        <v>14.259090909090908</v>
+        <v>14.291304347826086</v>
       </c>
       <c r="AR206" s="71" t="str">
         <f>IFERROR(VLOOKUP(A206,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29758,7 +30060,9 @@
       <c r="AG208" s="56">
         <v>16.3</v>
       </c>
-      <c r="AH208" s="56"/>
+      <c r="AH208" s="56">
+        <v>16.3</v>
+      </c>
       <c r="AI208" s="56"/>
       <c r="AJ208" s="56"/>
       <c r="AK208" s="56"/>
@@ -29768,11 +30072,11 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v>15.304347826086957</v>
+        <v>15.345833333333333</v>
       </c>
       <c r="AR208" s="71" t="str">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29881,7 +30185,9 @@
       <c r="AG209" s="56">
         <v>12.55</v>
       </c>
-      <c r="AH209" s="56"/>
+      <c r="AH209" s="56">
+        <v>11</v>
+      </c>
       <c r="AI209" s="56"/>
       <c r="AJ209" s="56"/>
       <c r="AK209" s="56"/>
@@ -29891,11 +30197,11 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>11.104545454545457</v>
+        <v>11.100000000000003</v>
       </c>
       <c r="AR209" s="71" t="str">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30248,7 +30554,9 @@
       <c r="AG212" s="56">
         <v>26.75</v>
       </c>
-      <c r="AH212" s="56"/>
+      <c r="AH212" s="56">
+        <v>27.55</v>
+      </c>
       <c r="AI212" s="56"/>
       <c r="AJ212" s="56"/>
       <c r="AK212" s="56"/>
@@ -30258,11 +30566,11 @@
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ212" s="71">
         <f t="shared" si="10"/>
-        <v>28.140476190476193</v>
+        <v>28.113636363636363</v>
       </c>
       <c r="AR212" s="71" t="str">
         <f>IFERROR(VLOOKUP(A212,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30274,6 +30582,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="AH1:AH212" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="K5:AO212">
     <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>""</formula>
